--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -967,20 +967,20 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1038,9 +1038,9 @@
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1330,22 +1330,22 @@
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 105,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2417,17 +2417,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3162,15 +3162,15 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3228,9 +3228,9 @@
       <c r="I38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3301,9 +3301,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3885,9 +3885,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3958,9 +3958,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4184,15 +4184,15 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4542,9 +4542,9 @@
       <c r="I56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4905,11 +4905,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5051,11 +5051,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5191,17 +5191,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5491,22 +5491,22 @@
       <c r="I69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5629,17 +5629,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,78 +6034,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1403,9 @@
       <c r="I13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2279,9 +2279,9 @@
       <c r="I25" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2423,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2855,17 +2855,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3153,24 +3153,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3226,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4104,9 +4104,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4321,24 +4321,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4467,11 +4467,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4761,9 +4761,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4905,11 +4905,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5199,9 +5199,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5418,9 +5418,9 @@
       <c r="I68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5629,17 +5629,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6073,24 +6073,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6219,11 +6219,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6359,17 +6359,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,78 +6472,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L83" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1622,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1914,22 +1914,22 @@
       <c r="I20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 105,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3001,17 +3001,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3153,24 +3153,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3812,9 +3812,9 @@
       <c r="I46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3885,9 +3885,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4330,15 +4330,15 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4469,9 +4469,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4542,9 +4542,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4768,15 +4768,15 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5126,9 @@
       <c r="I64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5635,11 +5635,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5775,17 +5775,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6075,22 +6075,22 @@
       <c r="I77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6213,17 +6213,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,78 +6618,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +819,9 @@
       <c r="I5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,17 +957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1038,9 +1038,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
@@ -1989,20 +1989,20 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2060,9 +2060,9 @@
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2352,22 +2352,22 @@
       <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2928,17 +2928,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 105,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3810,24 +3810,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3877,17 +3877,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4184,15 +4184,15 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4250,9 +4250,9 @@
       <c r="I52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4323,9 +4323,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,17 +4461,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4768,15 +4768,15 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4907,9 +4907,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4980,9 +4980,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5045,17 +5045,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5206,15 +5206,15 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5564,9 +5564,9 @@
       <c r="I70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5927,11 +5927,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6213,17 +6213,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6513,22 +6513,22 @@
       <c r="I83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,78 +7056,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1257,9 +1257,9 @@
       <c r="I11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1622,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2277,24 +2277,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2425,9 +2425,9 @@
       <c r="I27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2928,17 +2928,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3301,9 +3301,9 @@
       <c r="I39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3877,17 +3877,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,24 +4175,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4321,11 +4321,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4461,17 +4461,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4768,15 +4768,15 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5045,17 +5045,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5126,9 +5126,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5343,24 +5343,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5416,11 +5416,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5562,11 +5562,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5708,11 +5708,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5783,9 +5783,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5927,11 +5927,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6221,9 +6221,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6365,11 +6365,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6440,9 +6440,9 @@
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6651,17 +6651,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6764,14 +6764,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,14 +6837,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,14 +6910,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,14 +6983,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7056,14 +7056,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7095,24 +7095,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,14 +7129,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7168,11 +7168,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,14 +7202,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7241,11 +7241,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7275,14 +7275,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,14 +7348,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7381,17 +7381,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7421,14 +7421,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,78 +7494,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L97" s="2" t="n">
+      <c r="L99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,9 +892,9 @@
       <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1403,9 @@
       <c r="I13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,17 +2344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>▼ 66,7%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3522,20 +3522,20 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3960,20 +3960,20 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4096,17 +4096,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,24 +4175,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4252,20 +4252,20 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4315,17 +4315,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,24 +4467,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4688,9 +4688,9 @@
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4759,24 +4759,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4899,17 +4899,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5060,15 +5060,15 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5191,17 +5191,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5272,9 +5272,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5352,15 +5352,15 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5483,9 +5483,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5635,24 +5635,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>66,7%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5710,9 +5710,9 @@
       <c r="I72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5783,9 +5783,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5854,11 +5854,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5927,11 +5927,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6146,11 +6146,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6221,9 +6221,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6365,11 +6365,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6584,11 +6584,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6657,11 +6657,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6730,11 +6730,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6797,17 +6797,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6876,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7086,33 +7086,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,33 +7232,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7391,20 +7391,20 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7527,17 +7527,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,78 +7640,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L99" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,9 +892,9 @@
       <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1111,9 +1111,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,9 +1322,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1692,47 +1692,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,7 +1774,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1837,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1916,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,7 +1989,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1994,15 +1998,15 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2062,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2133,9 +2137,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2271,17 +2275,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2354,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2418,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2500,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2564,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2573,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,13 +2640,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2676,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2783,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2792,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,11 +2865,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,9 +2940,9 @@
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3084,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3447,9 +3451,9 @@
       <c r="I41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3585,17 +3589,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3629,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,7 +3732,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,24 +3741,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3810,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3883,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3956,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4027,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4096,17 +4100,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4170,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4248,24 +4252,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4316,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,17 +4392,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4462,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,24 +4471,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4505,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4540,24 +4544,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4578,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4613,11 +4617,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4651,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4686,11 +4690,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4724,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4759,11 +4763,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,12 +4797,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4832,11 +4836,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4899,17 +4903,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,12 +4943,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4980,9 +4984,9 @@
       <c r="I62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5000,7 +5004,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,7 +5046,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5051,24 +5055,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5118,17 +5122,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5197,11 +5201,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5265,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5343,11 +5347,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5377,12 +5381,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,7 +5411,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5416,24 +5420,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5483,17 +5487,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5562,11 +5566,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5596,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,7 +5630,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5635,24 +5639,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5708,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5781,11 +5785,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5848,17 +5852,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5888,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5927,11 +5931,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5961,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,7 +5995,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6000,24 +6004,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6067,17 +6071,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6107,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6148,9 +6152,9 @@
       <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6180,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6219,24 +6223,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6292,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6365,7 +6369,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6399,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6440,9 +6444,9 @@
       <c r="I82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6513,9 +6517,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6545,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6584,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6618,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6651,17 +6655,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6691,12 +6695,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6730,7 +6734,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6752,7 +6756,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6764,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,7 +6798,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6803,24 +6807,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6876,11 +6880,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6910,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6949,11 +6953,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6983,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7022,11 +7026,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7044,7 +7048,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7056,12 +7060,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7089,17 +7093,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7129,12 +7133,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7168,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7202,12 +7206,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,33 +7236,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,12 +7279,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7314,11 +7318,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,12 +7352,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,7 +7382,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7389,22 +7393,22 @@
       <c r="I95" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7425,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7460,11 +7464,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,12 +7498,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7533,11 +7537,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7567,12 +7571,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7610,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,12 +7644,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7679,11 +7683,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7713,12 +7717,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7754,9 +7758,9 @@
       <c r="I100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7786,12 +7790,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7819,17 +7823,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7859,12 +7863,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7898,7 +7902,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7932,78 +7936,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +963,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 31,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,5%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1401,24 +1401,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 141,7%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1629,15 +1629,15 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,59 +1684,55 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 84,2%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1764,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 850,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1916,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2062,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2129,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2202,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2315,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2354,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2427,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2461,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2500,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2534,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2567,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2640,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2710,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2753,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2865,24 +2861,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2899,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2929,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2938,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3005,17 +3001,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3088,7 +3084,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3157,24 +3153,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3191,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3224,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3264,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3297,17 +3293,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3367,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3376,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3440,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3449,24 +3445,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3483,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3522,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3556,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3589,17 +3585,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3668,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3732,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3741,7 +3737,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3750,15 +3746,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3775,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3814,11 +3810,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3921,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3994,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4027,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4140,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4170,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4213,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4286,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4316,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4325,24 +4321,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4359,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4432,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4471,11 +4467,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4505,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4546,9 +4542,9 @@
       <c r="I56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4578,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4617,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4651,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4690,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4724,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4754,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4762,8 +4758,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>6</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4772,37 +4770,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4836,11 +4836,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4911,9 +4911,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4943,12 +4943,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4984,9 +4984,9 @@
       <c r="I62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5055,11 +5055,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5122,17 +5122,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5201,11 +5201,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5265,33 +5265,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5347,11 +5347,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5420,24 +5420,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5493,11 +5493,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5566,11 +5566,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5712,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5787,9 +5787,9 @@
       <c r="I73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5852,17 +5852,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6004,24 +6004,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6071,17 +6071,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6150,11 +6150,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6223,24 +6223,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6296,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6369,11 +6369,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6442,11 +6442,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6515,11 +6515,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6588,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6841,12 +6841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6880,11 +6880,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6955,9 +6955,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7026,11 +7026,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7133,12 +7133,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7236,33 +7236,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,12 +7279,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7318,11 +7318,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,12 +7352,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7391,24 +7391,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7458,9 +7458,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7537,11 +7537,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7610,24 +7610,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7683,11 +7683,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7756,11 +7756,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7863,12 +7863,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7902,11 +7902,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8048,11 +8048,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8188,17 +8188,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8267,11 +8267,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8331,33 +8331,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8486,24 +8486,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8705,11 +8705,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8778,11 +8778,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -8812,12 +8812,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8845,17 +8845,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8885,12 +8885,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8918,17 +8918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8988,33 +8988,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9070,24 +9070,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9104,12 +9104,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9134,33 +9134,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9216,11 +9216,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9289,24 +9289,24 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9362,11 +9362,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9469,12 +9469,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9510,9 +9510,9 @@
       <c r="I124" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9542,12 +9542,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9575,17 +9575,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9654,11 +9654,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9688,78 +9688,3144 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>66,7%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -811,22 +811,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,6%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,5%</t>
+          <t>▼ 31,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1468,22 +1468,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 141,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 141,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1687,17 +1687,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 84,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 850,0%</t>
+          <t>▲ 84,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>19</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 850,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2419,20 +2419,20 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2852,25 +2852,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2930,20 +2930,20 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3080,24 +3080,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3220,9 +3220,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3518,24 +3518,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3958,9 +3958,9 @@
       <c r="I48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4102,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4388,17 +4388,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4469,9 +4469,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4686,24 +4686,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4758,10 +4758,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4770,41 +4768,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4836,11 +4832,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4870,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4900,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4908,8 +4904,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4918,37 +4916,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5276,9 +5276,9 @@
       <c r="I66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5381,14 +5381,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5420,11 +5420,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5527,14 +5527,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5566,11 +5566,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,14 +5600,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5641,9 +5641,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5673,14 +5673,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5712,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,14 +5746,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5785,11 +5785,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5892,14 +5892,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6006,9 +6006,9 @@
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,14 +6038,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6077,11 +6077,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,14 +6111,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6150,11 +6150,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6257,14 +6257,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6296,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6442,11 +6442,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6517,9 +6517,9 @@
       <c r="I83" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6549,14 +6549,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6588,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,14 +6622,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6655,17 +6655,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6695,14 +6695,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6768,14 +6768,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6798,33 +6798,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6841,14 +6841,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6882,9 +6882,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,14 +6914,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6953,24 +6953,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6987,14 +6987,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7026,11 +7026,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,14 +7060,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7093,17 +7093,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7133,14 +7133,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,14 +7206,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7236,33 +7236,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,14 +7279,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7318,11 +7318,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,14 +7352,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7382,33 +7382,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,14 +7425,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7458,17 +7458,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,14 +7498,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7537,24 +7537,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,14 +7571,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7601,33 +7601,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7685,9 +7685,9 @@
       <c r="I99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7717,14 +7717,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7756,24 +7756,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7790,14 +7790,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7829,11 +7829,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7863,14 +7863,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7902,11 +7902,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7936,14 +7936,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7975,11 +7975,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8009,14 +8009,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8048,11 +8048,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8082,14 +8082,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8155,14 +8155,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8188,17 +8188,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,14 +8228,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8267,11 +8267,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8301,14 +8301,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8331,33 +8331,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8374,14 +8374,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8447,14 +8447,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8477,33 +8477,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8561,9 +8561,9 @@
       <c r="I111" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8593,14 +8593,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8632,24 +8632,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8666,14 +8666,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8705,11 +8705,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8739,14 +8739,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8778,11 +8778,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8812,14 +8812,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8851,11 +8851,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8885,14 +8885,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8918,17 +8918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8958,14 +8958,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8997,11 +8997,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9031,14 +9031,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9061,33 +9061,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9104,14 +9104,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9137,17 +9137,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9177,14 +9177,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9216,24 +9216,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9250,14 +9250,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9280,33 +9280,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9323,14 +9323,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9362,11 +9362,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9396,14 +9396,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9435,24 +9435,24 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9469,14 +9469,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9542,14 +9542,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9581,11 +9581,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9615,14 +9615,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9654,11 +9654,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9688,14 +9688,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9721,17 +9721,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9761,14 +9761,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9800,11 +9800,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
@@ -9834,14 +9834,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9864,33 +9864,33 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -9980,14 +9980,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10028,15 +10028,15 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10053,14 +10053,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10126,12 +10126,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10272,14 +10272,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10305,17 +10305,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10345,14 +10345,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10386,9 +10386,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10418,14 +10418,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10448,33 +10448,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10491,14 +10491,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10530,11 +10530,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10564,14 +10564,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10603,24 +10603,24 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10637,14 +10637,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10676,11 +10676,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10710,14 +10710,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10749,11 +10749,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10783,14 +10783,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10822,11 +10822,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10856,14 +10856,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -10929,14 +10929,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10968,11 +10968,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11002,14 +11002,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11043,9 +11043,9 @@
       <c r="I145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11075,14 +11075,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11114,11 +11114,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11148,14 +11148,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11187,11 +11187,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11221,14 +11221,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11260,11 +11260,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11294,14 +11294,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11367,14 +11367,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11406,11 +11406,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11440,14 +11440,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11481,9 +11481,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11513,14 +11513,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11552,11 +11552,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11586,14 +11586,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11625,11 +11625,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11700,9 +11700,9 @@
       <c r="I154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11732,14 +11732,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11771,11 +11771,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11805,14 +11805,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11844,11 +11844,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -11878,14 +11878,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11911,17 +11911,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11951,14 +11951,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11990,11 +11990,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12024,14 +12024,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12054,33 +12054,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12097,14 +12097,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12136,11 +12136,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12170,14 +12170,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12200,33 +12200,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12243,14 +12243,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12282,11 +12282,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12316,14 +12316,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12355,24 +12355,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12389,14 +12389,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12428,11 +12428,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12462,14 +12462,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12501,11 +12501,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12574,11 +12574,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12608,14 +12608,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12641,17 +12641,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12681,14 +12681,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12720,11 +12720,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12754,78 +12754,224 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L169" s="2" t="n">
+      <c r="L171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -662,20 +662,20 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -957,22 +957,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1268,11 +1268,11 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,6%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,5%</t>
+          <t>▼ 31,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1614,22 +1614,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 141,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 141,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 84,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 850,0%</t>
+          <t>▲ 84,2%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2127,20 +2127,20 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>19</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 850,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2204,24 +2204,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2344,17 +2344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2782,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2998,25 +2998,25 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3076,20 +3076,20 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3226,24 +3226,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3366,9 +3366,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,24 +3737,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4104,9 +4104,9 @@
       <c r="I50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4175,11 +4175,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4534,17 +4534,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4615,9 +4615,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4759,11 +4759,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4832,24 +4832,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4904,10 +4904,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4916,41 +4914,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4982,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5016,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5046,7 +5042,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5054,8 +5050,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5064,37 +5062,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5422,9 +5422,9 @@
       <c r="I68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5527,14 +5527,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5566,11 +5566,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5673,14 +5673,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5712,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,14 +5746,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5787,9 +5787,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5819,14 +5819,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5858,11 +5858,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,14 +5892,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6038,14 +6038,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6077,11 +6077,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6152,9 +6152,9 @@
       <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6184,14 +6184,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6257,14 +6257,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6296,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6442,11 +6442,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6549,14 +6549,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6588,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6663,9 +6663,9 @@
       <c r="I85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6695,14 +6695,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6768,14 +6768,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6801,17 +6801,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6841,14 +6841,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6914,14 +6914,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6944,33 +6944,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6987,14 +6987,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7028,9 +7028,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,14 +7060,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7099,24 +7099,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7133,14 +7133,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,14 +7206,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7239,17 +7239,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7279,14 +7279,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7318,11 +7318,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,14 +7352,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7382,33 +7382,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7425,14 +7425,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7464,11 +7464,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,14 +7498,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7528,33 +7528,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,14 +7571,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7604,17 +7604,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7644,14 +7644,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7683,24 +7683,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7717,14 +7717,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7747,33 +7747,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7831,9 +7831,9 @@
       <c r="I101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7863,14 +7863,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7902,24 +7902,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7936,14 +7936,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7975,11 +7975,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8009,14 +8009,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8048,11 +8048,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8082,14 +8082,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8155,14 +8155,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8194,11 +8194,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,14 +8228,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8267,11 +8267,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8301,14 +8301,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8334,17 +8334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8374,14 +8374,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8447,14 +8447,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8477,33 +8477,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8520,14 +8520,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8593,14 +8593,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8623,33 +8623,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8707,9 +8707,9 @@
       <c r="I113" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8739,14 +8739,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8778,24 +8778,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8812,14 +8812,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8851,11 +8851,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8885,14 +8885,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8924,11 +8924,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8958,14 +8958,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8997,11 +8997,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9031,14 +9031,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9064,17 +9064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9104,14 +9104,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9143,11 +9143,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9177,14 +9177,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9207,33 +9207,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9250,14 +9250,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9283,17 +9283,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9323,14 +9323,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9362,24 +9362,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9396,14 +9396,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9426,33 +9426,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9469,14 +9469,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9542,14 +9542,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9581,24 +9581,24 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9615,14 +9615,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9654,11 +9654,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9688,14 +9688,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9727,11 +9727,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9761,14 +9761,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9800,11 +9800,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9834,14 +9834,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9867,17 +9867,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9907,14 +9907,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9946,11 +9946,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -9980,14 +9980,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10010,33 +10010,33 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10126,14 +10126,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10174,15 +10174,15 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10199,14 +10199,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10272,12 +10272,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10418,14 +10418,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10451,17 +10451,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10491,14 +10491,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10532,9 +10532,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10564,14 +10564,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10594,33 +10594,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10637,14 +10637,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10676,11 +10676,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10710,14 +10710,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10749,24 +10749,24 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10783,14 +10783,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10822,11 +10822,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10856,14 +10856,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10895,11 +10895,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10929,14 +10929,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10968,11 +10968,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11002,14 +11002,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11075,14 +11075,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11114,11 +11114,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11148,14 +11148,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11189,9 +11189,9 @@
       <c r="I147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11221,14 +11221,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11260,11 +11260,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11294,14 +11294,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11333,11 +11333,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11367,14 +11367,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11406,11 +11406,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11440,14 +11440,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11513,14 +11513,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11552,11 +11552,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11586,14 +11586,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11627,9 +11627,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11659,14 +11659,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11698,11 +11698,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11732,14 +11732,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11771,11 +11771,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11846,9 +11846,9 @@
       <c r="I156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11878,14 +11878,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11917,11 +11917,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11951,14 +11951,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11990,11 +11990,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12024,14 +12024,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12057,17 +12057,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,9%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12097,14 +12097,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12136,11 +12136,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12170,14 +12170,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12200,33 +12200,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12243,14 +12243,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12282,11 +12282,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12316,14 +12316,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12346,33 +12346,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12389,14 +12389,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12428,11 +12428,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12462,14 +12462,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12501,24 +12501,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12574,11 +12574,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12608,14 +12608,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12647,11 +12647,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12681,14 +12681,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12720,11 +12720,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12754,14 +12754,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12787,17 +12787,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12827,14 +12827,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12866,11 +12866,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12900,78 +12900,224 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L171" s="2" t="n">
+      <c r="L173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -808,20 +808,20 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1103,22 +1103,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,5%</t>
+        <v>13</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 31,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1760,22 +1760,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 141,7%</t>
+          <t>▼ 34,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1839,24 +1839,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 141,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -1979,17 +1979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 84,2%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 850,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 84,2%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2273,20 +2273,20 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 850,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 57,1%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2490,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2928,17 +2928,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3512,9 +3512,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3810,24 +3810,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4175,11 +4175,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4250,9 +4250,9 @@
       <c r="I52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4321,11 +4321,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4394,11 +4394,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4680,17 +4680,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4761,9 +4761,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4905,11 +4905,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4978,24 +4978,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5050,10 +5050,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5062,41 +5060,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5128,11 +5124,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5162,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5192,7 +5188,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5200,8 +5196,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5210,37 +5208,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5568,9 +5568,9 @@
       <c r="I70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5673,14 +5673,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5712,11 +5712,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5819,14 +5819,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5858,11 +5858,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,14 +5892,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -5933,9 +5933,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5965,14 +5965,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6004,11 +6004,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,14 +6038,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6077,11 +6077,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6184,14 +6184,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6298,9 +6298,9 @@
       <c r="I80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,14 +6330,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6369,11 +6369,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6442,11 +6442,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6549,14 +6549,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6588,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6695,14 +6695,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6809,9 +6809,9 @@
       <c r="I87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6841,14 +6841,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6880,11 +6880,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,14 +6914,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -6947,17 +6947,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6987,14 +6987,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7060,14 +7060,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7090,33 +7090,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7133,14 +7133,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7174,9 +7174,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7206,14 +7206,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7245,24 +7245,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,14 +7279,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7318,11 +7318,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7352,14 +7352,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7385,17 +7385,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7425,14 +7425,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7464,11 +7464,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,14 +7498,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7528,33 +7528,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7571,14 +7571,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7610,11 +7610,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7644,14 +7644,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7674,33 +7674,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7717,14 +7717,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7750,17 +7750,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7790,14 +7790,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7829,24 +7829,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7863,14 +7863,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -7893,33 +7893,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7977,9 +7977,9 @@
       <c r="I103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8009,14 +8009,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8048,24 +8048,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8082,14 +8082,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8121,11 +8121,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8155,14 +8155,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8194,11 +8194,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,14 +8228,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8267,11 +8267,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8301,14 +8301,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8340,11 +8340,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8374,14 +8374,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8447,14 +8447,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8480,17 +8480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8520,14 +8520,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8593,14 +8593,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8623,33 +8623,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,7%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8666,14 +8666,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8705,11 +8705,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8739,14 +8739,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8769,33 +8769,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8812,12 +8812,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8853,9 +8853,9 @@
       <c r="I115" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8885,14 +8885,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8924,24 +8924,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8958,14 +8958,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -8997,11 +8997,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9031,14 +9031,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9070,11 +9070,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9104,14 +9104,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9143,11 +9143,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>1</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9177,14 +9177,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9210,17 +9210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9250,14 +9250,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9289,11 +9289,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9323,14 +9323,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9353,33 +9353,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9396,14 +9396,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9429,17 +9429,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9469,14 +9469,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9508,24 +9508,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9542,14 +9542,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9572,33 +9572,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9615,14 +9615,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9654,11 +9654,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9688,14 +9688,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9727,24 +9727,24 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9761,14 +9761,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9800,11 +9800,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9834,14 +9834,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9873,11 +9873,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9907,14 +9907,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -9946,11 +9946,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9980,14 +9980,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10013,17 +10013,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10053,14 +10053,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10092,11 +10092,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10126,14 +10126,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10156,33 +10156,33 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L133" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10272,14 +10272,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10320,15 +10320,15 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10345,14 +10345,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10418,12 +10418,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10491,12 +10491,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10564,14 +10564,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10597,17 +10597,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10637,14 +10637,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10678,9 +10678,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10710,14 +10710,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10740,33 +10740,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10783,14 +10783,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10822,11 +10822,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10856,14 +10856,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -10895,24 +10895,24 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10929,14 +10929,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -10968,11 +10968,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11002,14 +11002,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11041,11 +11041,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11075,14 +11075,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11114,11 +11114,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11148,14 +11148,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11221,14 +11221,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11260,11 +11260,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11294,14 +11294,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11335,9 +11335,9 @@
       <c r="I149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11367,14 +11367,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11406,11 +11406,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11440,14 +11440,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11479,11 +11479,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11513,14 +11513,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11552,11 +11552,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11586,14 +11586,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11659,14 +11659,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11698,11 +11698,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11732,14 +11732,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11773,9 +11773,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11805,14 +11805,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11844,11 +11844,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11878,14 +11878,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -11917,11 +11917,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -11992,9 +11992,9 @@
       <c r="I158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12024,14 +12024,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12063,11 +12063,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12097,14 +12097,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12136,11 +12136,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12170,14 +12170,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12203,17 +12203,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
+        <v>3</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12243,14 +12243,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12282,11 +12282,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
@@ -12316,14 +12316,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12346,33 +12346,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12389,14 +12389,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12428,11 +12428,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12462,14 +12462,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12492,33 +12492,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12574,11 +12574,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12608,14 +12608,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12647,24 +12647,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12681,14 +12681,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12720,11 +12720,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12754,14 +12754,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12793,11 +12793,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12827,14 +12827,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12866,11 +12866,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12900,14 +12900,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -12933,17 +12933,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12973,14 +12973,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>BRINQ-042</t>
@@ -13012,11 +13012,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13046,78 +13046,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-042</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Bingo 24 cartelas</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>3534488839</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 39,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="L173" s="2" t="n">
+      <c r="L175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
+++ b/saida_skus/SKU_BRINQ-042-BINGO-24-CARTELAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,20 +954,20 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -976,11 +976,11 @@
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,20 +1392,20 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,20 +1538,20 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 31,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,5%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,22 +1833,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 141,7%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1998,11 +1998,11 @@
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 84,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 850,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,16 +2423,16 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 57,1%</t>
+        <v>29</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 141,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2563,17 +2563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>35</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 84,2%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2857,20 +2857,20 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 850,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 57,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,16 +3372,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3806,20 +3806,20 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3883,16 +3883,16 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,24 +4175,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4242,13 +4242,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4315,17 +4315,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4394,24 +4394,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4476,15 +4476,15 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4615,9 +4615,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4688,9 +4688,9 @@
       <c r="I58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4826,13 +4826,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4978,24 +4978,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5126,9 +5126,9 @@
       <c r="I64" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5196,10 +5196,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5208,39 +5206,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5274,11 +5270,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5381,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5414,9 +5410,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5454,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5495,9 +5491,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5527,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5557,7 +5553,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5568,22 +5564,22 @@
       <c r="I70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5600,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5639,7 +5635,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5673,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5712,9 +5708,9 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -5746,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5776,7 +5772,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5784,8 +5780,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5794,37 +5792,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5858,11 +5858,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6004,11 +6004,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6079,9 +6079,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6184,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6257,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6296,11 +6296,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6371,9 +6371,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6444,9 +6444,9 @@
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6515,11 +6515,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6588,11 +6588,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6661,11 +6661,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6807,11 +6807,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6882,9 +6882,9 @@
       <c r="I88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6953,11 +6953,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7026,11 +7026,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7133,12 +7133,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7206,12 +7206,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7245,24 +7245,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7279,12 +7279,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7352,12 +7352,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7391,11 +7391,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7466,9 +7466,9 @@
       <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7531,17 +7531,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7610,11 +7610,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7674,33 +7674,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7756,11 +7756,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7831,9 +7831,9 @@
       <c r="I101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7896,17 +7896,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7975,11 +7975,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8048,24 +8048,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8115,17 +8115,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8194,11 +8194,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8258,33 +8258,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8340,11 +8340,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8413,24 +8413,24 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8480,17 +8480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8623,33 +8623,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8705,11 +8705,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8769,33 +8769,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,7%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8812,12 +8812,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8851,11 +8851,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8885,12 +8885,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 105,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8924,24 +8924,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8997,11 +8997,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9070,9 +9070,9 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>▼ 66,7%</t>
         </is>
@@ -9104,12 +9104,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9145,9 +9145,9 @@
       <c r="I119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9210,17 +9210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9289,11 +9289,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9353,33 +9353,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 35,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9437,9 +9437,9 @@
       <c r="I123" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9469,12 +9469,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 105,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9508,24 +9508,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9542,12 +9542,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9575,17 +9575,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       <c r="I126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>▼ 66,7%</t>
         </is>
@@ -9688,12 +9688,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9727,24 +9727,24 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
       <c r="I128" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>▲ 50,0%</t>
         </is>
@@ -9834,12 +9834,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9873,11 +9873,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9940,9 +9940,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10019,11 +10019,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10092,24 +10092,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10159,17 +10159,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▼ 91,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10238,11 +10238,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10311,16 +10311,16 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
@@ -10345,12 +10345,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10384,11 +10384,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10491,12 +10491,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10530,11 +10530,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10605,9 +10605,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10637,12 +10637,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10676,11 +10676,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10743,17 +10743,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,7%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10822,11 +10822,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -10856,12 +10856,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -10904,15 +10904,15 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11043,9 +11043,9 @@
       <c r="I145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11116,9 +11116,9 @@
       <c r="I146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11148,12 +11148,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11221,12 +11221,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11260,11 +11260,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11294,12 +11294,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11327,17 +11327,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11406,11 +11406,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11440,12 +11440,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11479,24 +11479,24 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11552,11 +11552,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11625,11 +11625,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11698,11 +11698,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11732,12 +11732,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11805,12 +11805,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11844,11 +11844,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11878,12 +11878,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11919,9 +11919,9 @@
       <c r="I157" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12024,12 +12024,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12063,11 +12063,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12136,11 +12136,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12209,11 +12209,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12243,12 +12243,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12282,11 +12282,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
@@ -12316,12 +12316,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12349,17 +12349,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▼ 61,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12428,11 +12428,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12462,12 +12462,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12492,33 +12492,33 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12535,12 +12535,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12574,11 +12574,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12647,24 +12647,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12720,11 +12720,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12793,11 +12793,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12827,12 +12827,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12866,11 +12866,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12933,17 +12933,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 61,9%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13012,11 +13012,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13046,12 +13046,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13076,33 +13076,33 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 97,00</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L173" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13158,11 +13158,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13192,12 +13192,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -13231,16 +13231,16 @@
         </is>
       </c>
       <c r="I175" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L175" s="2" t="n">
@@ -13262,8 +13262,592 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3363535141</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-042</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Bingo 24 cartelas</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>3534488839</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>